--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,32 +429,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sistema Afetado</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CPE Base</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ID CVE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data Publicação</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Score CVSS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Descrição Técnica</t>
         </is>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,2238 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cpe:2.3:h:juniper:mx_series</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CVE-2026-0203</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>An Improper Handling of Exceptional Conditions vulnerability in packet processing of Juniper Networks Junos OS allows an unauthenticated, network-adjacent attacker sending a specifically malformed ICMP packet to cause an FPC to crash and restart, resulting in a Denial of Service (DoS).
+When an ICMP packet is received with a specifically malformed IP header value, the FPC receiving the packet crashes and restarts. Due to the specific type of malformed packet, adjacent upstream routers would not forward the packet, limiting the attack surface to adjacent networks.
+This issue only affects ICMPv4. ICMPv6 is not vulnerable to this issue.
+This issue does not affect AFT-based line cards such as the MPC10, MPC11, LC4800, LC9600, and MX304.
+This issue affects Junos OS: 
+  *  all versions before 21.2R3-S9, 
+  *  from 21.4 before 21.4R3-S10, 
+  *  from 22.2 before 22.2R3-S7, 
+  *  from 22.3 before 22.3R3-S4, 
+  *  from 22.4 before 22.4R3-S5, 
+  *  from 23.2 before 23.2R2-S3, 
+  *  from 23.4 before 23.4R2-S3, 
+  *  from 24.2 before 24.2R1-S2, 24.2R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CVE-2026-0877</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CVE-2026-0878</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Graphics: CanvasWebGL component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CVE-2026-0879</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CVE-2026-0880</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to integer overflow in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CVE-2026-0881</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Messaging System component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CVE-2026-0882</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Use-after-free in the IPC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CVE-2026-0883</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Information disclosure in the Networking component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CVE-2026-0884</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CVE-2026-0885</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CVE-2026-0886</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CVE-2026-0887</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Clickjacking issue, information disclosure in the PDF Viewer component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CVE-2026-0888</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Information disclosure in the XML component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CVE-2026-0889</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the DOM: Service Workers component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CVE-2026-0890</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the DOM: Copy &amp; Paste and Drag &amp; Drop component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CVE-2026-0891</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.6, Thunderbird ESR 140.6, Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CVE-2026-0892</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CVE-2026-24868</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the Privacy: Anti-Tracking component. This vulnerability affects Firefox &lt; 147.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CVE-2026-24869</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Layout: Scrolling and Overflow component. This vulnerability affects Firefox &lt; 147.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CVE-2020-37190</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Top Password Firefox Password Recovery 2.8 contains a denial of service vulnerability that allows attackers to crash the application by overflowing input fields. Attackers can trigger the vulnerability by inserting 5000 characters into the User Name or Registration Code input fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CVE-2026-2032</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Malicious scripts that interrupt new tab page loading could cause desynchronization between the address bar and page content, allowing the attacker to spoof arbitrary HTML under a trusted domain. This vulnerability affects Firefox for iOS &lt; 147.2.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CVE-2026-2447</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Heap buffer overflow in libvpx. This vulnerability affects Firefox &lt; 147.0.4, Firefox ESR &lt; 140.7.1, Firefox ESR &lt; 115.32.1, Thunderbird &lt; 140.7.2, and Thunderbird &lt; 147.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CVE-2026-2634</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Malicious scripts could cause desynchronization between the address bar and web content before a response is received in Firefox iOS, allowing attacker-controlled pages to be presented under spoofed domains. This vulnerability affects Firefox for iOS &lt; 147.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CVE-2026-2757</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the WebRTC: Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CVE-2026-2758</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CVE-2026-2759</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CVE-2026-2760</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CVE-2026-2761</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CVE-2026-2762</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Integer overflow in the JavaScript: Standard Library component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CVE-2026-2763</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CVE-2026-2764</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JIT miscompilation, use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CVE-2026-2765</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CVE-2026-2766</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CVE-2026-2767</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CVE-2026-2768</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CVE-2026-2769</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CVE-2026-2770</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Bindings (WebIDL) component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CVE-2026-2771</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Undefined behavior in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CVE-2026-2772</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Audio/Video: Playback component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CVE-2026-2773</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Web Audio component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CVE-2026-2774</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Integer overflow in the Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CVE-2026-2775</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: HTML Parser component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CVE-2026-2776</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Telemetry component in External Software. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CVE-2026-2777</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Messaging System component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CVE-2026-2778</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CVE-2026-2779</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CVE-2026-2780</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CVE-2026-2781</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Integer overflow in the Libraries component in NSS. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CVE-2026-2782</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CVE-2026-2783</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Information disclosure due to JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CVE-2026-2784</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CVE-2026-2785</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Invalid pointer in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CVE-2026-2786</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CVE-2026-2787</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Window and Location component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CVE-2026-2788</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: GMP component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CVE-2026-2789</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CVE-2026-2790</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Same-origin policy bypass in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CVE-2026-2791</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the Networking: Cache component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CVE-2026-2792</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CVE-2026-2793</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.32, Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CVE-2026-2794</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Information disclosure due to uninitialized memory in Firefox and Firefox Focus for Android. This vulnerability affects Firefox &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CVE-2026-2795</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CVE-2026-2796</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CVE-2026-2797</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CVE-2026-2798</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CVE-2026-2799</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CVE-2026-2800</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the WebAuthn component in Firefox for Android. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CVE-2026-2801</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CVE-2026-2802</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Race condition in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CVE-2026-2803</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Information disclosure, mitigation bypass in the Settings UI component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CVE-2026-2804</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CVE-2026-2805</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Invalid pointer in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CVE-2026-2806</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Uninitialized memory in the Graphics: Text component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:mozilla:firefox</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CVE-2026-2807</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -461,11 +461,7 @@
           <t>CVE-2026-3845</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Heap buffer overflow in the Audio/Video: Playback component in Firefox for Android. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -483,11 +479,7 @@
           <t>CVE-2026-3846</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the CSS Parsing and Computation component. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -505,11 +497,7 @@
           <t>CVE-2026-3847</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 148.0.2. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148.0.2.</t>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -461,11 +461,7 @@
           <t>CVE-2025-60007</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>A NULL Pointer Dereference vulnerability in the chassis daemon (chassisd) of Juniper Networks Junos OS on MX, SRX and EX Series allows a local attacker with low privileges to cause a Denial-of-Service (DoS).
@@ -491,11 +487,7 @@
           <t>CVE-2026-0203</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>An Improper Handling of Exceptional Conditions vulnerability in packet processing of Juniper Networks Junos OS allows an unauthenticated, network-adjacent attacker sending a specifically malformed ICMP packet to cause an FPC to crash and restart, resulting in a Denial of Service (DoS).
@@ -525,11 +517,7 @@
           <t>CVE-2026-21905</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>A Loop with Unreachable Exit Condition ('Infinite Loop') vulnerability in the SIP application layer gateway (ALG) of Juniper Networks Junos OS on SRX Series and MX Series with MX-SPC3 or MS-MPC allows an unauthenticated network-based attacker sending specific SIP messages over TCP to crash the flow management process, leading to a Denial of Service (DoS).
@@ -558,11 +546,7 @@
           <t>CVE-2026-21912</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>A Time-of-check Time-of-use (TOCTOU) Race Condition vulnerability in the method to collect FPC Ethernet firmware statistics of Juniper Networks Junos OS on MX10k Series allows a local, low-privileged attacker executing the 'show system firmware' CLI command to cause an LC480 or LC2101 line card to reset.
@@ -588,11 +572,7 @@
           <t>CVE-2026-21918</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>A Double Free vulnerability in the flow processing daemon (flowd) of Juniper Networks Junos OS on SRX and MX Series allows an unauthenticated, network-based attacker to cause a Denial-of-Service (DoS). On all SRX and MX Series platforms, when during TCP session establishment a specific sequence of packets is encountered a double free happens. This causes flowd to crash and the respective FPC to restart.
@@ -615,11 +595,7 @@
           <t>CVE-2026-23086</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>In the Linux kernel, the following vulnerability has been resolved:
@@ -688,11 +664,7 @@
           <t>CVE-2026-0877</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -710,11 +682,7 @@
           <t>CVE-2026-0878</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics: CanvasWebGL component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -732,11 +700,7 @@
           <t>CVE-2026-0879</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -754,11 +718,7 @@
           <t>CVE-2026-0880</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Sandbox escape due to integer overflow in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -776,11 +736,7 @@
           <t>CVE-2026-0881</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Sandbox escape in the Messaging System component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -798,11 +754,7 @@
           <t>CVE-2026-0882</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Use-after-free in the IPC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -820,11 +772,7 @@
           <t>CVE-2026-0883</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Information disclosure in the Networking component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -842,11 +790,7 @@
           <t>CVE-2026-0884</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -864,11 +808,7 @@
           <t>CVE-2026-0885</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -886,11 +826,7 @@
           <t>CVE-2026-0886</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -908,11 +844,7 @@
           <t>CVE-2026-0887</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Clickjacking issue, information disclosure in the PDF Viewer component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -930,11 +862,7 @@
           <t>CVE-2026-0888</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Information disclosure in the XML component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -952,11 +880,7 @@
           <t>CVE-2026-0889</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Denial-of-service in the DOM: Service Workers component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -974,11 +898,7 @@
           <t>CVE-2026-0890</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Spoofing issue in the DOM: Copy &amp; Paste and Drag &amp; Drop component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -996,11 +916,7 @@
           <t>CVE-2026-0891</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.6, Thunderbird ESR 140.6, Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -1018,11 +934,7 @@
           <t>CVE-2026-0892</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -1040,11 +952,7 @@
           <t>CVE-2026-24868</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Privacy: Anti-Tracking component. This vulnerability affects Firefox &lt; 147.0.2.</t>
@@ -1062,11 +970,7 @@
           <t>CVE-2026-24869</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>Use-after-free in the Layout: Scrolling and Overflow component. This vulnerability affects Firefox &lt; 147.0.2.</t>
@@ -1084,11 +988,7 @@
           <t>CVE-2020-37190</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Top Password Firefox Password Recovery 2.8 contains a denial of service vulnerability that allows attackers to crash the application by overflowing input fields. Attackers can trigger the vulnerability by inserting 5000 characters into the User Name or Registration Code input fields.</t>
@@ -1106,11 +1006,7 @@
           <t>CVE-2026-2032</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>Malicious scripts that interrupt new tab page loading could cause desynchronization between the address bar and page content, allowing the attacker to spoof arbitrary HTML under a trusted domain. This vulnerability affects Firefox for iOS &lt; 147.2.1.</t>
@@ -1128,11 +1024,7 @@
           <t>CVE-2026-2447</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>Heap buffer overflow in libvpx. This vulnerability affects Firefox &lt; 147.0.4, Firefox ESR &lt; 140.7.1, Firefox ESR &lt; 115.32.1, Thunderbird &lt; 140.7.2, and Thunderbird &lt; 147.0.2.</t>
@@ -1150,11 +1042,7 @@
           <t>CVE-2026-2634</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>Malicious scripts could cause desynchronization between the address bar and web content before a response is received in Firefox iOS, allowing attacker-controlled pages to be presented under spoofed domains. This vulnerability affects Firefox for iOS &lt; 147.4.</t>
@@ -1172,11 +1060,7 @@
           <t>CVE-2026-2757</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC: Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1194,11 +1078,7 @@
           <t>CVE-2026-2758</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1216,11 +1096,7 @@
           <t>CVE-2026-2759</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1238,11 +1114,7 @@
           <t>CVE-2026-2760</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1260,11 +1132,7 @@
           <t>CVE-2026-2761</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>Sandbox escape in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1282,11 +1150,7 @@
           <t>CVE-2026-2762</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Integer overflow in the JavaScript: Standard Library component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1304,11 +1168,7 @@
           <t>CVE-2026-2763</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1326,11 +1186,7 @@
           <t>CVE-2026-2764</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>JIT miscompilation, use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1348,11 +1204,7 @@
           <t>CVE-2026-2765</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1370,11 +1222,7 @@
           <t>CVE-2026-2766</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1392,11 +1240,7 @@
           <t>CVE-2026-2767</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1414,11 +1258,7 @@
           <t>CVE-2026-2768</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>Sandbox escape in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1436,11 +1276,7 @@
           <t>CVE-2026-2769</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>Use-after-free in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1458,11 +1294,7 @@
           <t>CVE-2026-2770</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Bindings (WebIDL) component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1480,11 +1312,7 @@
           <t>CVE-2026-2771</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Undefined behavior in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1502,11 +1330,7 @@
           <t>CVE-2026-2772</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>Use-after-free in the Audio/Video: Playback component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1524,11 +1348,7 @@
           <t>CVE-2026-2773</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Web Audio component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1546,11 +1366,7 @@
           <t>CVE-2026-2774</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>Integer overflow in the Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1568,11 +1384,7 @@
           <t>CVE-2026-2775</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: HTML Parser component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1590,11 +1402,7 @@
           <t>CVE-2026-2776</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Telemetry component in External Software. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1612,11 +1420,7 @@
           <t>CVE-2026-2777</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Privilege escalation in the Messaging System component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1634,11 +1438,7 @@
           <t>CVE-2026-2778</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1656,11 +1456,7 @@
           <t>CVE-2026-2779</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1678,11 +1474,7 @@
           <t>CVE-2026-2780</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1700,11 +1492,7 @@
           <t>CVE-2026-2781</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>Integer overflow in the Libraries component in NSS. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1722,11 +1510,7 @@
           <t>CVE-2026-2782</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1744,11 +1528,7 @@
           <t>CVE-2026-2783</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Information disclosure due to JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1766,11 +1546,7 @@
           <t>CVE-2026-2784</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1788,11 +1564,7 @@
           <t>CVE-2026-2785</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>Invalid pointer in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1810,11 +1582,7 @@
           <t>CVE-2026-2786</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1832,11 +1600,7 @@
           <t>CVE-2026-2787</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Window and Location component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1854,11 +1618,7 @@
           <t>CVE-2026-2788</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: GMP component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1876,11 +1636,7 @@
           <t>CVE-2026-2789</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Use-after-free in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1898,11 +1654,7 @@
           <t>CVE-2026-2790</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1920,11 +1672,7 @@
           <t>CVE-2026-2791</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Networking: Cache component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1942,11 +1690,7 @@
           <t>CVE-2026-2792</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1964,11 +1708,7 @@
           <t>CVE-2026-2793</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.32, Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1986,11 +1726,7 @@
           <t>CVE-2026-2794</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Information disclosure due to uninitialized memory in Firefox and Firefox Focus for Android. This vulnerability affects Firefox &lt; 148.</t>
@@ -2008,11 +1744,7 @@
           <t>CVE-2026-2795</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2030,11 +1762,7 @@
           <t>CVE-2026-2796</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>JIT miscompilation in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2052,11 +1780,7 @@
           <t>CVE-2026-2797</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2074,11 +1798,7 @@
           <t>CVE-2026-2798</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2096,11 +1816,7 @@
           <t>CVE-2026-2799</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2118,11 +1834,7 @@
           <t>CVE-2026-2800</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>Spoofing issue in the WebAuthn component in Firefox for Android. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2140,11 +1852,7 @@
           <t>CVE-2026-2801</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2162,11 +1870,7 @@
           <t>CVE-2026-2802</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>Race condition in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2184,11 +1888,7 @@
           <t>CVE-2026-2803</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>Information disclosure, mitigation bypass in the Settings UI component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2206,11 +1906,7 @@
           <t>CVE-2026-2804</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2228,11 +1924,7 @@
           <t>CVE-2026-2805</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Invalid pointer in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2250,11 +1942,7 @@
           <t>CVE-2026-2806</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>Uninitialized memory in the Graphics: Text component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2272,11 +1960,7 @@
           <t>CVE-2026-2807</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2294,11 +1978,7 @@
           <t>CVE-2026-3845</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Heap buffer overflow in the Audio/Video: Playback component in Firefox for Android. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -2316,11 +1996,7 @@
           <t>CVE-2026-3846</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the CSS Parsing and Computation component. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -2338,11 +2014,7 @@
           <t>CVE-2026-3847</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 148.0.2. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148.0.2.</t>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +471,7 @@
           <t>2026-01-15T21:16:03.780</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A NULL Pointer Dereference vulnerability in the chassis daemon (chassisd) of Juniper Networks Junos OS on MX, SRX and EX Series allows a local attacker with low privileges to cause a Denial-of-Service (DoS).
@@ -506,11 +502,7 @@
           <t>2026-01-15T21:16:05.457</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>An Improper Handling of Exceptional Conditions vulnerability in packet processing of Juniper Networks Junos OS allows an unauthenticated, network-adjacent attacker sending a specifically malformed ICMP packet to cause an FPC to crash and restart, resulting in a Denial of Service (DoS).
@@ -545,11 +537,7 @@
           <t>2026-01-15T21:16:05.990</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>A Loop with Unreachable Exit Condition ('Infinite Loop') vulnerability in the SIP application layer gateway (ALG) of Juniper Networks Junos OS on SRX Series and MX Series with MX-SPC3 or MS-MPC allows an unauthenticated network-based attacker sending specific SIP messages over TCP to crash the flow management process, leading to a Denial of Service (DoS).
@@ -583,11 +571,7 @@
           <t>2026-01-15T21:16:07.357</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>A Time-of-check Time-of-use (TOCTOU) Race Condition vulnerability in the method to collect FPC Ethernet firmware statistics of Juniper Networks Junos OS on MX10k Series allows a local, low-privileged attacker executing the 'show system firmware' CLI command to cause an LC480 or LC2101 line card to reset.
@@ -618,11 +602,7 @@
           <t>2026-01-15T21:16:08.050</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>A Double Free vulnerability in the flow processing daemon (flowd) of Juniper Networks Junos OS on SRX and MX Series allows an unauthenticated, network-based attacker to cause a Denial-of-Service (DoS). On all SRX and MX Series platforms, when during TCP session establishment a specific sequence of packets is encountered a double free happens. This causes flowd to crash and the respective FPC to restart.
@@ -650,11 +630,7 @@
           <t>2026-02-04T17:16:19.467</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>In the Linux kernel, the following vulnerability has been resolved:
@@ -728,11 +704,7 @@
           <t>2026-01-13T14:16:38.270</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -755,11 +727,7 @@
           <t>2026-01-13T14:16:38.367</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics: CanvasWebGL component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -782,11 +750,7 @@
           <t>2026-01-13T14:16:38.463</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -809,11 +773,7 @@
           <t>2026-01-13T14:16:38.557</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Sandbox escape due to integer overflow in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -836,11 +796,7 @@
           <t>2026-01-13T14:16:38.657</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Sandbox escape in the Messaging System component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -863,11 +819,7 @@
           <t>2026-01-13T14:16:38.750</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Use-after-free in the IPC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -890,11 +842,7 @@
           <t>2026-01-13T14:16:38.853</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Information disclosure in the Networking component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -917,11 +865,7 @@
           <t>2026-01-13T14:16:38.950</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -944,11 +888,7 @@
           <t>2026-01-13T14:16:39.050</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -971,11 +911,7 @@
           <t>2026-01-13T14:16:39.140</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 115.32, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -998,11 +934,7 @@
           <t>2026-01-13T14:16:39.240</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Clickjacking issue, information disclosure in the PDF Viewer component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -1025,11 +957,7 @@
           <t>2026-01-13T14:16:39.340</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Information disclosure in the XML component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -1052,11 +980,7 @@
           <t>2026-01-13T14:16:39.437</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Denial-of-service in the DOM: Service Workers component. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -1079,11 +1003,7 @@
           <t>2026-01-13T14:16:39.523</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Spoofing issue in the DOM: Copy &amp; Paste and Drag &amp; Drop component. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -1106,11 +1026,7 @@
           <t>2026-01-13T14:16:39.627</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.6, Thunderbird ESR 140.6, Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147, Firefox ESR &lt; 140.7, Thunderbird &lt; 147, and Thunderbird &lt; 140.7.</t>
@@ -1133,11 +1049,7 @@
           <t>2026-01-13T14:16:39.723</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 146 and Thunderbird 146. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 147 and Thunderbird &lt; 147.</t>
@@ -1160,11 +1072,7 @@
           <t>2026-01-27T16:16:36.173</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Privacy: Anti-Tracking component. This vulnerability affects Firefox &lt; 147.0.2.</t>
@@ -1187,11 +1095,7 @@
           <t>2026-01-27T16:16:36.283</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Use-after-free in the Layout: Scrolling and Overflow component. This vulnerability affects Firefox &lt; 147.0.2.</t>
@@ -1214,11 +1118,7 @@
           <t>2026-02-11T21:16:13.093</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Top Password Firefox Password Recovery 2.8 contains a denial of service vulnerability that allows attackers to crash the application by overflowing input fields. Attackers can trigger the vulnerability by inserting 5000 characters into the User Name or Registration Code input fields.</t>
@@ -1241,11 +1141,7 @@
           <t>2026-02-16T15:18:34.620</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Malicious scripts that interrupt new tab page loading could cause desynchronization between the address bar and page content, allowing the attacker to spoof arbitrary HTML under a trusted domain. This vulnerability affects Firefox for iOS &lt; 147.2.1.</t>
@@ -1268,11 +1164,7 @@
           <t>2026-02-16T15:18:34.740</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Heap buffer overflow in libvpx. This vulnerability affects Firefox &lt; 147.0.4, Firefox ESR &lt; 140.7.1, Firefox ESR &lt; 115.32.1, Thunderbird &lt; 140.7.2, and Thunderbird &lt; 147.0.2.</t>
@@ -1295,11 +1187,7 @@
           <t>2026-02-24T14:16:23.810</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Malicious scripts could cause desynchronization between the address bar and web content before a response is received in Firefox iOS, allowing attacker-controlled pages to be presented under spoofed domains. This vulnerability affects Firefox for iOS &lt; 147.4.</t>
@@ -1322,11 +1210,7 @@
           <t>2026-02-24T14:16:23.927</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC: Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1349,11 +1233,7 @@
           <t>2026-02-24T14:16:24.037</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1376,11 +1256,7 @@
           <t>2026-02-24T14:16:24.147</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1403,11 +1279,7 @@
           <t>2026-02-24T14:16:24.257</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1430,11 +1302,7 @@
           <t>2026-02-24T14:16:24.370</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Sandbox escape in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1457,11 +1325,7 @@
           <t>2026-02-24T14:16:24.480</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Integer overflow in the JavaScript: Standard Library component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1484,11 +1348,7 @@
           <t>2026-02-24T14:16:24.620</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1511,11 +1371,7 @@
           <t>2026-02-24T14:16:24.737</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>JIT miscompilation, use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1538,11 +1394,7 @@
           <t>2026-02-24T14:16:24.860</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1565,11 +1417,7 @@
           <t>2026-02-24T14:16:24.973</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1592,11 +1440,7 @@
           <t>2026-02-24T14:16:25.080</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1619,11 +1463,7 @@
           <t>2026-02-24T14:16:25.183</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Sandbox escape in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1646,11 +1486,7 @@
           <t>2026-02-24T14:16:25.287</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Use-after-free in the Storage: IndexedDB component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1673,11 +1509,7 @@
           <t>2026-02-24T14:16:25.397</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Bindings (WebIDL) component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1700,11 +1532,7 @@
           <t>2026-02-24T14:16:25.497</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Undefined behavior in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1727,11 +1555,7 @@
           <t>2026-02-24T14:16:25.603</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Use-after-free in the Audio/Video: Playback component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1754,11 +1578,7 @@
           <t>2026-02-24T14:16:25.703</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Web Audio component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1781,11 +1601,7 @@
           <t>2026-02-24T14:16:25.810</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Integer overflow in the Audio/Video component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1808,11 +1624,7 @@
           <t>2026-02-24T14:16:25.917</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: HTML Parser component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1835,11 +1647,7 @@
           <t>2026-02-24T14:16:26.023</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Telemetry component in External Software. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1862,11 +1670,7 @@
           <t>2026-02-24T14:16:26.123</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Privilege escalation in the Messaging System component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1889,11 +1693,7 @@
           <t>2026-02-24T14:16:26.230</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1916,11 +1716,7 @@
           <t>2026-02-24T14:16:26.330</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1943,11 +1739,7 @@
           <t>2026-02-24T14:16:26.437</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1970,11 +1762,7 @@
           <t>2026-02-24T14:16:26.533</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Integer overflow in the Libraries component in NSS. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -1997,11 +1785,7 @@
           <t>2026-02-24T14:16:26.640</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2024,11 +1808,7 @@
           <t>2026-02-24T14:16:26.747</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Information disclosure due to JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2051,11 +1831,7 @@
           <t>2026-02-24T14:16:26.847</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2078,11 +1854,7 @@
           <t>2026-02-24T14:16:26.950</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Invalid pointer in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2105,11 +1877,7 @@
           <t>2026-02-24T14:16:27.053</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2132,11 +1900,7 @@
           <t>2026-02-24T14:16:27.157</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Window and Location component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2159,11 +1923,7 @@
           <t>2026-02-24T14:16:27.260</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: GMP component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2186,11 +1946,7 @@
           <t>2026-02-24T14:16:27.370</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Use-after-free in the Graphics: ImageLib component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2213,11 +1969,7 @@
           <t>2026-02-24T14:16:27.473</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the Networking: JAR component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2240,11 +1992,7 @@
           <t>2026-02-24T14:16:27.580</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Networking: Cache component. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2267,11 +2015,7 @@
           <t>2026-02-24T14:16:27.680</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2294,11 +2038,7 @@
           <t>2026-02-24T14:16:27.787</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.32, Firefox ESR 140.7, Thunderbird ESR 140.7, Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148, Firefox ESR &lt; 115.33, Firefox ESR &lt; 140.8, Thunderbird &lt; 148, and Thunderbird &lt; 140.8.</t>
@@ -2321,11 +2061,7 @@
           <t>2026-02-24T14:16:27.897</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Information disclosure due to uninitialized memory in Firefox and Firefox Focus for Android. This vulnerability affects Firefox &lt; 148.</t>
@@ -2348,11 +2084,7 @@
           <t>2026-02-24T14:16:28.000</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2375,11 +2107,7 @@
           <t>2026-02-24T14:16:28.100</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>JIT miscompilation in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2402,11 +2130,7 @@
           <t>2026-02-24T14:16:28.200</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2429,11 +2153,7 @@
           <t>2026-02-24T14:16:28.307</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2456,11 +2176,7 @@
           <t>2026-02-24T14:16:28.400</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2483,11 +2199,7 @@
           <t>2026-02-24T14:16:28.503</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Spoofing issue in the WebAuthn component in Firefox for Android. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2510,11 +2222,7 @@
           <t>2026-02-24T14:16:28.610</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2537,11 +2245,7 @@
           <t>2026-02-24T14:16:28.703</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Race condition in the JavaScript: GC component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2564,11 +2268,7 @@
           <t>2026-02-24T14:16:28.810</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Information disclosure, mitigation bypass in the Settings UI component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2591,11 +2291,7 @@
           <t>2026-02-24T14:16:28.917</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2618,11 +2314,7 @@
           <t>2026-02-24T14:16:29.010</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Invalid pointer in the DOM: Core &amp; HTML component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2645,11 +2337,7 @@
           <t>2026-02-24T14:16:29.113</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Uninitialized memory in the Graphics: Text component. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2672,11 +2360,7 @@
           <t>2026-02-24T14:16:29.220</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 147 and Thunderbird 147. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148 and Thunderbird &lt; 148.</t>
@@ -2699,11 +2383,7 @@
           <t>2026-03-10T18:19:05.507</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Heap buffer overflow in the Audio/Video: Playback component in Firefox for Android. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -2726,11 +2406,7 @@
           <t>2026-03-10T18:19:05.673</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the CSS Parsing and Computation component. This vulnerability affects Firefox &lt; 148.0.2.</t>
@@ -2753,14 +2429,64 @@
           <t>2026-03-10T18:19:05.837</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 148.0.2. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CVE-2026-3888</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-03-17T14:16:17.410</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox 148.0.2. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 148.0.2.</t>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Local privilege escalation in snapd on Linux allows local attackers to get root privilege by re-creating snap's private /tmp directory when systemd-tmpfiles is configured to automatically clean up this directory. This issue affects Ubuntu 16.04 LTS, 18.04 LTS, 20.04 LTS, 22.04 LTS, and 24.04 LTS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CVE-2026-32617</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-03-16T14:19:39.630</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AnythingLLM is an application that turns pieces of content into context that any LLM can use as references during chatting. In 1.11.1 and earlier, On default installations where no password or API key has been configured, all HTTP endpoints and the agent WebSocket lack authentication, and the server's CORS policy accepts any origin. AnythingLLM Desktop binds to 127.0.0.1 (loopback) by default. Modern browsers (Chrome, Edge, Firefox) implement Private Network Access (PNA). This explicitly blocks public websites from making requests to local IP addresses. Exploitation is only viable from within the same local network (LAN) due to browser-level blocking of public-to-private requests.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,11 +2452,7 @@
           <t>2026-03-17T14:16:17.410</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Local privilege escalation in snapd on Linux allows local attackers to get root privilege by re-creating snap's private /tmp directory when systemd-tmpfiles is configured to automatically clean up this directory. This issue affects Ubuntu 16.04 LTS, 18.04 LTS, 20.04 LTS, 22.04 LTS, and 24.04 LTS.</t>
@@ -2479,14 +2475,1225 @@
           <t>2026-03-16T14:19:39.630</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>AnythingLLM is an application that turns pieces of content into context that any LLM can use as references during chatting. In 1.11.1 and earlier, On default installations where no password or API key has been configured, all HTTP endpoints and the agent WebSocket lack authentication, and the server's CORS policy accepts any origin. AnythingLLM Desktop binds to 127.0.0.1 (loopback) by default. Modern browsers (Chrome, Edge, Firefox) implement Private Network Access (PNA). This explicitly blocks public websites from making requests to local IP addresses. Exploitation is only viable from within the same local network (LAN) due to browser-level blocking of public-to-private requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CVE-2026-4684</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.210</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Race condition, use-after-free in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CVE-2026-4685</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.323</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CVE-2026-4686</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.440</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CVE-2026-4687</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.537</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Telemetry component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CVE-2026-4688</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.640</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to use-after-free in the Disability Access APIs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CVE-2026-4689</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.737</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions, integer overflow in the XPCOM component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CVE-2026-4690</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.837</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions, integer overflow in the XPCOM component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CVE-2026-4691</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:04.937</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Use-after-free in the CSS Parsing and Computation component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CVE-2026-4692</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.040</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Responsive Design Mode component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CVE-2026-4693</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.143</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: Playback component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CVE-2026-4694</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.247</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions, integer overflow in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CVE-2026-4695</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.473</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CVE-2026-4696</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.590</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Layout: Text and Fonts component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CVE-2026-4697</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.687</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CVE-2026-4698</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.783</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CVE-2026-4699</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:05.900</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Layout: Text and Fonts component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CVE-2026-4700</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.003</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the Networking: HTTP component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CVE-2026-4701</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.103</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CVE-2026-4702</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.207</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVE-2026-4704</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.303</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVE-2026-4705</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.403</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Undefined behavior in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CVE-2026-4706</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.503</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CVE-2026-4707</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.603</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CVE-2026-4708</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.707</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CVE-2026-4709</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.810</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: GMP component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CVE-2026-4710</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:06.910</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CVE-2026-4711</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.010</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Widget: Cocoa component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CVE-2026-4712</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.107</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Information disclosure in the Widget: Cocoa component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CVE-2026-4713</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.217</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CVE-2026-4714</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.313</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CVE-2026-4715</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.410</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Uninitialized memory in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CVE-2026-4716</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.503</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions, uninitialized memory in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CVE-2026-4717</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.600</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CVE-2026-4718</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Undefined behavior in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CVE-2026-4719</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.793</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Text component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CVE-2026-4720</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.893</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.8, Thunderbird ESR 140.8, Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CVE-2026-4721</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:07.990</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.33, Firefox ESR 140.8, Thunderbird ESR 140.8, Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CVE-2026-4722</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.093</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the IPC component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CVE-2026-4723</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.190</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CVE-2026-4724</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.280</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Undefined behavior in the Audio/Video component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CVE-2026-4725</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.377</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to use-after-free in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CVE-2026-4726</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.473</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the XML component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CVE-2026-4727</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.570</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the Libraries component in NSS. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CVE-2026-4728</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.680</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the Privacy: Anti-Tracking component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CVE-2026-4729</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:16:08.830</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2498,11 +2498,7 @@
           <t>2026-03-24T13:16:04.210</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Race condition, use-after-free in the Graphics: WebRender component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2525,11 +2521,7 @@
           <t>2026-03-24T13:16:04.323</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2552,11 +2544,7 @@
           <t>2026-03-24T13:16:04.440</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2579,11 +2567,7 @@
           <t>2026-03-24T13:16:04.537</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Telemetry component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2606,11 +2590,7 @@
           <t>2026-03-24T13:16:04.640</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Sandbox escape due to use-after-free in the Disability Access APIs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2633,11 +2613,7 @@
           <t>2026-03-24T13:16:04.737</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions, integer overflow in the XPCOM component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2660,11 +2636,7 @@
           <t>2026-03-24T13:16:04.837</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions, integer overflow in the XPCOM component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2687,11 +2659,7 @@
           <t>2026-03-24T13:16:04.937</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Use-after-free in the CSS Parsing and Computation component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2714,11 +2682,7 @@
           <t>2026-03-24T13:16:05.040</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Sandbox escape in the Responsive Design Mode component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2741,11 +2705,7 @@
           <t>2026-03-24T13:16:05.143</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: Playback component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2768,11 +2728,7 @@
           <t>2026-03-24T13:16:05.247</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions, integer overflow in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2795,11 +2751,7 @@
           <t>2026-03-24T13:16:05.473</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2822,11 +2774,7 @@
           <t>2026-03-24T13:16:05.590</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Use-after-free in the Layout: Text and Fonts component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2849,11 +2797,7 @@
           <t>2026-03-24T13:16:05.687</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2876,11 +2820,7 @@
           <t>2026-03-24T13:16:05.783</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2903,11 +2843,7 @@
           <t>2026-03-24T13:16:05.900</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Layout: Text and Fonts component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2930,11 +2866,7 @@
           <t>2026-03-24T13:16:06.003</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Networking: HTTP component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2957,11 +2889,7 @@
           <t>2026-03-24T13:16:06.103</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -2984,11 +2912,7 @@
           <t>2026-03-24T13:16:06.207</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>JIT miscompilation in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3011,11 +2935,7 @@
           <t>2026-03-24T13:16:06.303</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Denial-of-service in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3038,11 +2958,7 @@
           <t>2026-03-24T13:16:06.403</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Undefined behavior in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3065,11 +2981,7 @@
           <t>2026-03-24T13:16:06.503</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3092,11 +3004,7 @@
           <t>2026-03-24T13:16:06.603</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3119,11 +3027,7 @@
           <t>2026-03-24T13:16:06.707</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3146,11 +3050,7 @@
           <t>2026-03-24T13:16:06.810</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: GMP component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3173,11 +3073,7 @@
           <t>2026-03-24T13:16:06.910</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3200,11 +3096,7 @@
           <t>2026-03-24T13:16:07.010</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Use-after-free in the Widget: Cocoa component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3227,11 +3119,7 @@
           <t>2026-03-24T13:16:07.107</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Information disclosure in the Widget: Cocoa component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3254,11 +3142,7 @@
           <t>2026-03-24T13:16:07.217</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3281,11 +3165,7 @@
           <t>2026-03-24T13:16:07.313</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3308,11 +3188,7 @@
           <t>2026-03-24T13:16:07.410</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Uninitialized memory in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3335,11 +3211,7 @@
           <t>2026-03-24T13:16:07.503</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions, uninitialized memory in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3362,11 +3234,7 @@
           <t>2026-03-24T13:16:07.600</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Privilege escalation in the Netmonitor component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3389,11 +3257,7 @@
           <t>2026-03-24T13:16:07.700</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Undefined behavior in the WebRTC: Signaling component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3416,11 +3280,7 @@
           <t>2026-03-24T13:16:07.793</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Text component. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3443,11 +3303,7 @@
           <t>2026-03-24T13:16:07.893</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.8, Thunderbird ESR 140.8, Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3470,11 +3326,7 @@
           <t>2026-03-24T13:16:07.990</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.33, Firefox ESR 140.8, Thunderbird ESR 140.8, Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149, Firefox ESR &lt; 115.34, Firefox ESR &lt; 140.9, Thunderbird &lt; 149, and Thunderbird &lt; 140.9.</t>
@@ -3497,11 +3349,7 @@
           <t>2026-03-24T13:16:08.093</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Privilege escalation in the IPC component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3524,11 +3372,7 @@
           <t>2026-03-24T13:16:08.190</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3551,11 +3395,7 @@
           <t>2026-03-24T13:16:08.280</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Undefined behavior in the Audio/Video component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3578,11 +3418,7 @@
           <t>2026-03-24T13:16:08.377</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Sandbox escape due to use-after-free in the Graphics: Canvas2D component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3605,11 +3441,7 @@
           <t>2026-03-24T13:16:08.473</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Denial-of-service in the XML component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3632,11 +3464,7 @@
           <t>2026-03-24T13:16:08.570</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Denial-of-service in the Libraries component in NSS. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3659,11 +3487,7 @@
           <t>2026-03-24T13:16:08.680</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Spoofing issue in the Privacy: Anti-Tracking component. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
@@ -3686,14 +3510,145 @@
           <t>2026-03-24T13:16:08.830</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CVE-2026-5731</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-04-07T13:16:47.347</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox 148 and Thunderbird 148. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149 and Thunderbird &lt; 149.</t>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.34.0, Firefox ESR 140.9.0, Thunderbird ESR 140.9.0, Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2, Firefox ESR &lt; 115.34.1, and Firefox ESR &lt; 140.9.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CVE-2026-5732</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-04-07T13:16:47.463</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions, integer overflow in the Graphics: Text component. This vulnerability affects Firefox &lt; 149.0.2 and Firefox ESR &lt; 140.9.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CVE-2026-5733</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-04-07T13:16:47.567</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: WebGPU component. This vulnerability affects Firefox &lt; 149.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CVE-2026-5734</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-04-07T13:16:47.667</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.9.0, Thunderbird ESR 140.9.0, Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2 and Firefox ESR &lt; 140.9.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CVE-2026-5735</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-04-07T13:16:47.763</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,11 +3533,7 @@
           <t>2026-04-07T13:16:47.347</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.34.0, Firefox ESR 140.9.0, Thunderbird ESR 140.9.0, Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2, Firefox ESR &lt; 115.34.1, and Firefox ESR &lt; 140.9.1.</t>
@@ -3560,11 +3556,7 @@
           <t>2026-04-07T13:16:47.463</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions, integer overflow in the Graphics: Text component. This vulnerability affects Firefox &lt; 149.0.2 and Firefox ESR &lt; 140.9.1.</t>
@@ -3587,11 +3579,7 @@
           <t>2026-04-07T13:16:47.567</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: WebGPU component. This vulnerability affects Firefox &lt; 149.0.2.</t>
@@ -3614,11 +3602,7 @@
           <t>2026-04-07T13:16:47.667</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.9.0, Thunderbird ESR 140.9.0, Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2 and Firefox ESR &lt; 140.9.1.</t>
@@ -3641,14 +3625,56 @@
           <t>2026-04-07T13:16:47.763</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CVE-2025-30650</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-04-08T19:24:00.440</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox 149.0.1 and Thunderbird 149.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability affects Firefox &lt; 149.0.2.</t>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>A Missing Authentication for Critical Function vulnerability in command processing of Juniper Networks Junos OS allows a privileged local attacker to gain access to line cards running Junos OS Evolved
+ as root.
+This issue affects systems running Junos OS using Linux-based line cards. Affected line cards include:
+  *  MPC7, MPC8, MPC9, MPC10, MPC11
+  *  LC2101, LC2103
+  *  LC480, LC4800, LC9600
+  *  MX304 (built-in FPC)
+  *  MX-SPC3
+  *  SRX5K-SPC3
+  *  EX9200-40XS
+  *  FPC3-PTX-U2, FPC3-PTX-U3
+  *  FPC3-SFF-PTX
+  *  LC1101, LC1102, LC1104, LC1105
+This issue affects Junos OS: 
+  *  all versions before 22.4R3-S8, 
+  *  from 23.2 before 23.2R2-S6, 
+  *  from 23.4 before 23.4R2-S6, 
+  *  from 24.2 before 24.2R2-S3, 
+  *  from 24.4 before 24.4R2,
+  *  from 25.2 before 25.2R2.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3648,11 +3648,7 @@
           <t>2026-04-08T19:24:00.440</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>A Missing Authentication for Critical Function vulnerability in command processing of Juniper Networks Junos OS allows a privileged local attacker to gain access to line cards running Junos OS Evolved
@@ -3678,6 +3674,190 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CVE-2026-33774</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-04-09T22:16:25.803</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>An Improper Check for Unusual or Exceptional Conditions vulnerability in the packet forwarding engine (pfe) of Juniper Networks Junos OS on MX Series allows an unauthenticated, network-based attacker to bypass the configured firewall filter and access the control-plane of the device.
+On MX platforms with 
+MPC10, MPC11, LC4800 or LC9600
+line cards, and MX304, firewall filters applied on a loopback interface lo0.n (where n is a non-0 number) don't get executed when lo0.n is in the global VRF / default routing-instance.
+ An affected configuration would be:
+user@host# show configuration interfaces lo0 | display set
+set interfaces lo0 unit 1 family inet filter input &lt;filter-name&gt;
+where a firewall filter is applied to a non-0 loopback interface, but that loopback interface is not referred to in any routing-instance (RI) configuration, which implies that it's used in the default RI.
+The issue can be observed with the CLI command:
+user@device&gt; show firewall counter filter &lt;filter_name&gt; 
+not showing any matches.
+This issue affects Junos OS on MX Series:
+  *  all versions before 23.2R2-S6,
+  *  23.4 versions before 23.4R2-S7,
+  *  24.2 versions before 24.2R2,
+  *  24.4 versions before 24.4R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CVE-2026-33775</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-04-09T22:16:26.020</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>A Missing Release of Memory after Effective Lifetime vulnerability in the BroadBand Edge subscriber management daemon (bbe-smgd) of Juniper Networks Junos OS on MX Series allows an adjacent, unauthenticated attacker to cause a Denial of Service (DoS).
+If the authentication packet-type option is configured and a received packet does not match that packet type, the memory leak occurs. When all memory 
+available to bbe-smgd has been consumed, no new subscribers will be able to login.
+The memory utilization of bbe-smgd can be monitored with the following show command:
+user@host&gt; show system processes extensive | match bbe-smgd
+The below log message can be observed when this limit has been reached:
+bbesmgd[&lt;PID&gt;]: %DAEMON-3-SMD_DPROF_RSMON_ERROR: Resource unavailability, Reason: Daemon Heap Memory exhaustion
+This issue affects Junos OS on MX Series:
+  *  all versions before 22.4R3-S8,
+  *  23.2 versions before 23.2R2-S5,
+  *  23.4 versions before 23.4R2-S6,
+  *  24.2 versions before 24.2R2-S2,
+  *  24.4 versions before 24.4R2,
+  *  25.2 versions before 25.2R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CVE-2026-33778</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-04-09T22:16:26.500</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>An Improper Validation of Syntactic Correctness of Input vulnerability in the  IPsec library used by kmd and iked of Juniper Networks Junos OS on SRX Series and MX Series allows an unauthenticated, network-based attacker to cause a complete Denial-of-Service (DoS).
+If an affected device receives a specifically malformed first ISAKMP packet from the initiator, the kmd/iked process will crash and restart, which momentarily prevents new security associations (SAs) for from being established. Repeated exploitation of this vulnerability causes a complete inability to establish new VPN connections.
+This issue affects Junos OS on 
+SRX Series and MX Series:
+  *  all versions before 22.4R3-S9,
+  *  23.2 version before 23.2R2-S6,
+  *  23.4 version before 23.4R2-S7,
+  *  24.2 versions before 24.2R2-S4,
+  *  24.4 versions before 24.4R2-S3,
+  *  25.2 versions before 25.2R1-S2, 25.2R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CVE-2026-33782</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-04-09T22:16:27.393</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>A Missing Release of Memory after Effective Lifetime vulnerability in the DHCP daemon (jdhcpd) of Juniper Networks Junos OS on MX Series, allows an adjacent, unauthenticated attacker to cause a memory leak, that will eventually cause a complete Denial-of-Service (DoS).
+In a DHCPv6 over PPPoE, or DHCPv6 over VLAN with Active lease query or Bulk lease query scenario, every subscriber logout will leak a small amount of memory. When all available memory has been exhausted, jdhcpd will crash and restart which causes a complete service impact until the process has recovered.
+The memory usage of jdhcpd can be monitored with:
+user@host&gt; show system processes extensive | match jdhcpd
+This issue affects Junos OS:
+  *  all versions before 22.4R3-S1,
+  *  23.2 versions before 23.2R2,
+  *  23.4 versions before 23.4R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Juniper MX Series</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CVE-2026-33785</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-04-09T22:16:27.987</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>A Missing Authorization vulnerability in the CLI of Juniper Networks Junos OS on MX Series allows a local, authenticated user with low privileges to execute specific commands which will lead to a complete compromise of managed devices.
+Any user logged in, without requiring specific privileges, can issue 'request csds' CLI operational commands. These commands are only meant to be executed by high privileged or users designated for Juniper Device Manager (JDM) / Connected Security Distributed Services (CSDS) operations as they will impact all aspects of the devices managed via the respective MX.
+This issue affects Junos OS on MX Series:
+  *  24.4 releases before 24.4R2-S3, 
+  *  25.2 releases before 25.2R2.
+This issue does not affect Junos OS releases before 24.4.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3690,11 +3690,7 @@
           <t>2026-04-09T22:16:25.803</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>An Improper Check for Unusual or Exceptional Conditions vulnerability in the packet forwarding engine (pfe) of Juniper Networks Junos OS on MX Series allows an unauthenticated, network-based attacker to bypass the configured firewall filter and access the control-plane of the device.
@@ -3732,11 +3728,7 @@
           <t>2026-04-09T22:16:26.020</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>A Missing Release of Memory after Effective Lifetime vulnerability in the BroadBand Edge subscriber management daemon (bbe-smgd) of Juniper Networks Junos OS on MX Series allows an adjacent, unauthenticated attacker to cause a Denial of Service (DoS).
@@ -3772,11 +3764,7 @@
           <t>2026-04-09T22:16:26.500</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>An Improper Validation of Syntactic Correctness of Input vulnerability in the  IPsec library used by kmd and iked of Juniper Networks Junos OS on SRX Series and MX Series allows an unauthenticated, network-based attacker to cause a complete Denial-of-Service (DoS).
@@ -3808,11 +3796,7 @@
           <t>2026-04-09T22:16:27.393</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>A Missing Release of Memory after Effective Lifetime vulnerability in the DHCP daemon (jdhcpd) of Juniper Networks Junos OS on MX Series, allows an adjacent, unauthenticated attacker to cause a memory leak, that will eventually cause a complete Denial-of-Service (DoS).
@@ -3842,11 +3826,7 @@
           <t>2026-04-09T22:16:27.987</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>A Missing Authorization vulnerability in the CLI of Juniper Networks Junos OS on MX Series allows a local, authenticated user with low privileges to execute specific commands which will lead to a complete compromise of managed devices.
@@ -3858,6 +3838,1059 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CVE-2026-6746</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:20.720</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CVE-2026-6747</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:20.813</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Use-after-free in the WebRTC component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CVE-2026-6748</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:20.910</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Uninitialized memory in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CVE-2026-6749</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:20.993</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Information disclosure due to uninitialized memory in the Graphics: Canvas2D component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CVE-2026-6750</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.073</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Graphics: WebRender component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CVE-2026-6751</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.163</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Uninitialized memory in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CVE-2026-6752</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.250</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CVE-2026-6753</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.340</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CVE-2026-6754</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.420</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript Engine component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CVE-2026-6755</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.510</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: postMessage component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CVE-2026-6756</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.593</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in Firefox for Android. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CVE-2026-6757</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.690</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Invalid pointer in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CVE-2026-6758</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.770</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CVE-2026-6759</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.857</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Use-after-free in the Widget: Cocoa component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CVE-2026-6760</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:21.950</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the Networking: Cookies component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CVE-2026-6761</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.040</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Networking component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CVE-2026-6762</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.137</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the DOM: Core &amp; HTML component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CVE-2026-6763</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.227</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the File Handling component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CVE-2026-6764</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.313</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the DOM: Device Interfaces component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CVE-2026-6765</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.390</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Information disclosure in the Form Autofill component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CVE-2026-6766</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.493</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Libraries component in NSS. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CVE-2026-6767</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.577</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Other issue in the Libraries component in NSS. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CVE-2026-6768</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.667</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the Networking: Cookies component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CVE-2026-6769</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.753</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Debugger component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CVE-2026-6770</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.840</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Other issue in the Storage: IndexedDB component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CVE-2026-6771</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:22.927</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CVE-2026-6772</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.007</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Libraries component in NSS. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CVE-2026-6773</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.087</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Denial-of-service due to integer overflow in the Graphics: WebGPU component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CVE-2026-6774</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.173</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CVE-2026-6775</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.260</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CVE-2026-6776</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.350</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the WebRTC: Networking component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CVE-2026-6777</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.430</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Other issue in the Networking: DNS component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CVE-2026-6778</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.513</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Invalid pointer in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CVE-2026-6779</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.600</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Other issue in the JavaScript Engine component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CVE-2026-6780</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.683</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CVE-2026-6781</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.770</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Denial-of-service in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CVE-2026-6782</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.847</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Information disclosure in the IP Protection component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CVE-2026-6783</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:23.930</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions, integer overflow in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CVE-2026-6784</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:24.020</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3854,11 +3854,7 @@
           <t>2026-04-21T13:16:20.720</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Core &amp; HTML component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -3881,11 +3877,7 @@
           <t>2026-04-21T13:16:20.813</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>Use-after-free in the WebRTC component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -3908,11 +3900,7 @@
           <t>2026-04-21T13:16:20.910</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Uninitialized memory in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -3935,11 +3923,7 @@
           <t>2026-04-21T13:16:20.993</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Information disclosure due to uninitialized memory in the Graphics: Canvas2D component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -3962,11 +3946,7 @@
           <t>2026-04-21T13:16:21.073</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Privilege escalation in the Graphics: WebRender component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -3989,11 +3969,7 @@
           <t>2026-04-21T13:16:21.163</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Uninitialized memory in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4016,11 +3992,7 @@
           <t>2026-04-21T13:16:21.250</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -4043,11 +4015,7 @@
           <t>2026-04-21T13:16:21.340</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4070,11 +4038,7 @@
           <t>2026-04-21T13:16:21.420</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript Engine component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -4097,11 +4061,7 @@
           <t>2026-04-21T13:16:21.510</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: postMessage component. This vulnerability was fixed in Firefox 150.</t>
@@ -4124,11 +4084,7 @@
           <t>2026-04-21T13:16:21.593</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Mitigation bypass in Firefox for Android. This vulnerability was fixed in Firefox 150.</t>
@@ -4151,11 +4107,7 @@
           <t>2026-04-21T13:16:21.690</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Invalid pointer in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4178,11 +4130,7 @@
           <t>2026-04-21T13:16:21.770</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150.</t>
@@ -4205,11 +4153,7 @@
           <t>2026-04-21T13:16:21.857</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Use-after-free in the Widget: Cocoa component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4232,11 +4176,7 @@
           <t>2026-04-21T13:16:21.950</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Networking: Cookies component. This vulnerability was fixed in Firefox 150.</t>
@@ -4259,11 +4199,7 @@
           <t>2026-04-21T13:16:22.040</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Privilege escalation in the Networking component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4286,11 +4222,7 @@
           <t>2026-04-21T13:16:22.137</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Spoofing issue in the DOM: Core &amp; HTML component. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -4313,11 +4245,7 @@
           <t>2026-04-21T13:16:22.227</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Mitigation bypass in the File Handling component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4340,11 +4268,7 @@
           <t>2026-04-21T13:16:22.313</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the DOM: Device Interfaces component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4367,11 +4291,7 @@
           <t>2026-04-21T13:16:22.390</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>Information disclosure in the Form Autofill component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4394,11 +4314,7 @@
           <t>2026-04-21T13:16:22.493</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Libraries component in NSS. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4421,11 +4337,7 @@
           <t>2026-04-21T13:16:22.577</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Other issue in the Libraries component in NSS. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -4448,11 +4360,7 @@
           <t>2026-04-21T13:16:22.667</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Mitigation bypass in the Networking: Cookies component. This vulnerability was fixed in Firefox 150.</t>
@@ -4475,11 +4383,7 @@
           <t>2026-04-21T13:16:22.753</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Privilege escalation in the Debugger component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4502,11 +4406,7 @@
           <t>2026-04-21T13:16:22.840</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Other issue in the Storage: IndexedDB component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4529,11 +4429,7 @@
           <t>2026-04-21T13:16:22.927</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4556,11 +4452,7 @@
           <t>2026-04-21T13:16:23.007</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Libraries component in NSS. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, and Firefox ESR 140.10.</t>
@@ -4583,11 +4475,7 @@
           <t>2026-04-21T13:16:23.087</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Denial-of-service due to integer overflow in the Graphics: WebGPU component. This vulnerability was fixed in Firefox 150.</t>
@@ -4610,11 +4498,7 @@
           <t>2026-04-21T13:16:23.173</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 150.</t>
@@ -4637,11 +4521,7 @@
           <t>2026-04-21T13:16:23.260</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC component. This vulnerability was fixed in Firefox 150.</t>
@@ -4664,11 +4544,7 @@
           <t>2026-04-21T13:16:23.350</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the WebRTC: Networking component. This vulnerability was fixed in Firefox 150 and Firefox ESR 140.10.</t>
@@ -4691,11 +4567,7 @@
           <t>2026-04-21T13:16:23.430</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Other issue in the Networking: DNS component. This vulnerability was fixed in Firefox 150.</t>
@@ -4718,11 +4590,7 @@
           <t>2026-04-21T13:16:23.513</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Invalid pointer in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
@@ -4745,11 +4613,7 @@
           <t>2026-04-21T13:16:23.600</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Other issue in the JavaScript Engine component. This vulnerability was fixed in Firefox 150.</t>
@@ -4772,11 +4636,7 @@
           <t>2026-04-21T13:16:23.683</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Denial-of-service in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
@@ -4799,11 +4659,7 @@
           <t>2026-04-21T13:16:23.770</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Denial-of-service in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
@@ -4826,11 +4682,7 @@
           <t>2026-04-21T13:16:23.847</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>Information disclosure in the IP Protection component. This vulnerability was fixed in Firefox 150.</t>
@@ -4853,11 +4705,7 @@
           <t>2026-04-21T13:16:23.930</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions, integer overflow in the Audio/Video: Playback component. This vulnerability was fixed in Firefox 150.</t>
@@ -4880,14 +4728,37 @@
           <t>2026-04-21T13:16:24.020</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CVE-2026-6786</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-04-21T13:16:24.250</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.</t>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4751,14 +4751,37 @@
           <t>2026-04-21T13:16:24.250</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CVE-2026-6785</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-04-26T19:53:39.010</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.34, Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4774,14 +4774,145 @@
           <t>2026-04-26T19:53:39.010</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.34, Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CVE-2026-7320</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:16:37.447</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox ESR 115.34, Firefox ESR 140.9, Thunderbird ESR 140.9, Firefox 149 and Thunderbird 149. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150, Firefox ESR 115.35, Firefox ESR 140.10, Thunderbird 150, and Thunderbird 140.10.</t>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Information disclosure due to incorrect boundary conditions in the Audio/Video component. This vulnerability was fixed in Firefox 150.0.1, Firefox ESR 140.10.1, and Firefox ESR 115.35.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CVE-2026-7321</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:16:37.550</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the WebRTC: Networking component. This vulnerability was fixed in Firefox ESR 140.10.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CVE-2026-7322</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:16:37.727</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.35.0, Firefox ESR 140.10.0, Thunderbird ESR 140.10.0, Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1, Firefox ESR 140.10.1, and Firefox ESR 115.35.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CVE-2026-7323</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:16:37.837</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.10.0, Thunderbird ESR 140.10.0, Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1 and Firefox ESR 140.10.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CVE-2026-7324</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:16:37.950</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4797,11 +4797,7 @@
           <t>2026-04-28T15:16:37.447</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Information disclosure due to incorrect boundary conditions in the Audio/Video component. This vulnerability was fixed in Firefox 150.0.1, Firefox ESR 140.10.1, and Firefox ESR 115.35.1.</t>
@@ -4824,11 +4820,7 @@
           <t>2026-04-28T15:16:37.550</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the WebRTC: Networking component. This vulnerability was fixed in Firefox ESR 140.10.1.</t>
@@ -4851,11 +4843,7 @@
           <t>2026-04-28T15:16:37.727</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.35.0, Firefox ESR 140.10.0, Thunderbird ESR 140.10.0, Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1, Firefox ESR 140.10.1, and Firefox ESR 115.35.1.</t>
@@ -4878,11 +4866,7 @@
           <t>2026-04-28T15:16:37.837</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.10.0, Thunderbird ESR 140.10.0, Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1 and Firefox ESR 140.10.1.</t>
@@ -4905,14 +4889,145 @@
           <t>2026-04-28T15:16:37.950</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CVE-2026-8090</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-05-07T13:16:13.967</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox 150.0.0 and Thunderbird 150.0.0. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.1.</t>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Networking component. This vulnerability was fixed in Firefox 150.0.2, Firefox ESR 140.10.2, and Firefox ESR 115.35.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CVE-2026-8091</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-05-07T13:16:14.087</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: Playback component. This vulnerability was fixed in Firefox ESR 140.10.2 and Firefox ESR 115.35.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CVE-2026-8092</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-05-07T13:16:14.203</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.35.1, Firefox ESR 140.10.1 and Firefox 150.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.2, Firefox ESR 140.10.2, and Firefox ESR 115.35.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CVE-2026-8093</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-05-07T13:16:14.317</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 150.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CVE-2026-8094</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-05-07T13:16:14.430</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Other issue in the WebRTC component. This vulnerability was fixed in Firefox ESR 140.10.2.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4912,11 +4912,7 @@
           <t>2026-05-07T13:16:13.967</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Networking component. This vulnerability was fixed in Firefox 150.0.2, Firefox ESR 140.10.2, and Firefox ESR 115.35.2.</t>
@@ -4939,11 +4935,7 @@
           <t>2026-05-07T13:16:14.087</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: Playback component. This vulnerability was fixed in Firefox ESR 140.10.2 and Firefox ESR 115.35.2.</t>
@@ -4966,11 +4958,7 @@
           <t>2026-05-07T13:16:14.203</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 115.35.1, Firefox ESR 140.10.1 and Firefox 150.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.2, Firefox ESR 140.10.2, and Firefox ESR 115.35.2.</t>
@@ -4993,11 +4981,7 @@
           <t>2026-05-07T13:16:14.317</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 150.0.1. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 150.0.2.</t>
@@ -5020,14 +5004,91 @@
           <t>2026-05-07T13:16:14.430</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Other issue in the WebRTC component. This vulnerability was fixed in Firefox ESR 140.10.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>CVE-2026-41431</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:16:34.280</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Other issue in the WebRTC component. This vulnerability was fixed in Firefox ESR 140.10.2.</t>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Zen is a firefox-based browser. Prior to 1.19.9b, Zen Browser ships a Mozilla Application Resource (MAR) updater (org.mozilla.updater) that has had all MAR signature verification stripped from the Firefox codebase it was forked from. The MAR files served to users contain zero cryptographic signatures, and the updater binary contains zero cryptographic verification code. This eliminates the defense-in-depth that MAR signing provides. If the update server or GitHub release pipeline is compromised, arbitrary unsigned code can be delivered to all Zen users via the auto-update mechanism. This vulnerability is fixed in 1.19.9b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>CVE-2026-44658</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:16:38.243</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Zen is a firefox-based browser. Prior to 1.19.12b, RSS feed URLs entered by the user are validated to http: or https: in promptForFeedUrl, but item links inside the feed are not subject to the same restriction. The provider maps each RSS/Atom item link into item.url, filters only for presence and date, and returns the item list. The live-folder manager later creates pinned lazy tabs from these values with gBrowser.addTrustedTab(item.url, ...). This vulnerability is fixed in 1.19.12b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CVE-2026-44659</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-05-11T18:16:38.380</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Zen is a firefox-based browser. Prior to 1.19.12b, the ZEN Browser incorrectly truncates long hostnames in the address bar and shows only the attacker-controlled prefix of the subdomain, hiding the actual registrable domain (eTLD+1). As a result, an attacker can craft extremely long malicious subdomains that visually imitate trusted brands, and the browser will display only the spoofed prefix, misleading users about the actual origin of the site. This directly compromises the URL bar as a security indicator and creates a phishing/supply-chain attack vector. This vulnerability is fixed in 1.19.12b.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5027,11 +5027,7 @@
           <t>2026-05-11T18:16:34.280</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Zen is a firefox-based browser. Prior to 1.19.9b, Zen Browser ships a Mozilla Application Resource (MAR) updater (org.mozilla.updater) that has had all MAR signature verification stripped from the Firefox codebase it was forked from. The MAR files served to users contain zero cryptographic signatures, and the updater binary contains zero cryptographic verification code. This eliminates the defense-in-depth that MAR signing provides. If the update server or GitHub release pipeline is compromised, arbitrary unsigned code can be delivered to all Zen users via the auto-update mechanism. This vulnerability is fixed in 1.19.9b.</t>
@@ -5054,11 +5050,7 @@
           <t>2026-05-11T18:16:38.243</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Zen is a firefox-based browser. Prior to 1.19.12b, RSS feed URLs entered by the user are validated to http: or https: in promptForFeedUrl, but item links inside the feed are not subject to the same restriction. The provider maps each RSS/Atom item link into item.url, filters only for presence and date, and returns the item list. The live-folder manager later creates pinned lazy tabs from these values with gBrowser.addTrustedTab(item.url, ...). This vulnerability is fixed in 1.19.12b.</t>
@@ -5081,14 +5073,145 @@
           <t>2026-05-11T18:16:38.380</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Zen is a firefox-based browser. Prior to 1.19.12b, the ZEN Browser incorrectly truncates long hostnames in the address bar and shows only the attacker-controlled prefix of the subdomain, hiding the actual registrable domain (eTLD+1). As a result, an attacker can craft extremely long malicious subdomains that visually imitate trusted brands, and the browser will display only the spoofed prefix, misleading users about the actual origin of the site. This directly compromises the URL bar as a security indicator and creates a phishing/supply-chain attack vector. This vulnerability is fixed in 1.19.12b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CVE-2026-8388</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-05-12T14:17:11.813</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Zen is a firefox-based browser. Prior to 1.19.12b, the ZEN Browser incorrectly truncates long hostnames in the address bar and shows only the attacker-controlled prefix of the subdomain, hiding the actual registrable domain (eTLD+1). As a result, an attacker can craft extremely long malicious subdomains that visually imitate trusted brands, and the browser will display only the spoofed prefix, misleading users about the actual origin of the site. This directly compromises the URL bar as a security indicator and creates a phishing/supply-chain attack vector. This vulnerability is fixed in 1.19.12b.</t>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 150.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>CVE-2026-8389</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-05-12T14:17:11.930</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 150.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CVE-2026-8390</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-05-12T14:17:12.050</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CVE-2026-8391</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-05-12T14:17:12.173</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Other issue in the JavaScript Engine component. This vulnerability was fixed in Firefox 150.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CVE-2026-8401</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-05-12T15:16:20.100</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Profile Backup component. This vulnerability was fixed in Firefox 150.0.3.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5096,11 +5096,7 @@
           <t>2026-05-12T14:17:11.813</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 150.0.3.</t>
@@ -5123,11 +5119,7 @@
           <t>2026-05-12T14:17:11.930</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 150.0.3.</t>
@@ -5150,11 +5142,7 @@
           <t>2026-05-12T14:17:12.050</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>Use-after-free in the JavaScript: WebAssembly component. This vulnerability was fixed in Firefox 150.0.3.</t>
@@ -5177,11 +5165,7 @@
           <t>2026-05-12T14:17:12.173</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Other issue in the JavaScript Engine component. This vulnerability was fixed in Firefox 150.0.3.</t>
@@ -5204,14 +5188,37 @@
           <t>2026-05-12T15:16:20.100</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Sandbox escape in the Profile Backup component. This vulnerability was fixed in Firefox 150.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CVE-2026-42177</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-05-12T18:17:24.240</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Sandbox escape in the Profile Backup component. This vulnerability was fixed in Firefox 150.0.3.</t>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>linux-entra-sso is a browser plugin for Linux to SSO on Microsoft Entra ID. Prior to 1.8.1, platform/chrome/js/platform-chrome.js:69-88 registers a single declarativeNetRequest rule whose urlFilter is Platform.SSO_URL + "/*", i.e. "https://login.microsoftonline.com/*". Chrome's urlFilter without a | or || anchor is substring-matched against the full request URL. The same applied rule action is modifyHeaders that attaches the Entra ID Primary Refresh Token cookie. The Firefox adapter in platform/firefox/js/platform-firefox.js:53 performs a belt-and-braces startsWith(Platform.SSO_URL) check before injecting the header; the Chrome adapter does not. When the extension holds broad host permissions through the optional_host_permissions: ["https://*/*"] declared in platform/chrome/manifest.json:34, a main-frame navigation to a URL whose path embeds https://login.microsoftonline.com/ causes Chrome to attach the PRT cookie to the request to the attacker-controlled host. This vulnerability is fixed in 1.8.1.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5211,14 +5211,847 @@
           <t>2026-05-12T18:17:24.240</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>linux-entra-sso is a browser plugin for Linux to SSO on Microsoft Entra ID. Prior to 1.8.1, platform/chrome/js/platform-chrome.js:69-88 registers a single declarativeNetRequest rule whose urlFilter is Platform.SSO_URL + "/*", i.e. "https://login.microsoftonline.com/*". Chrome's urlFilter without a | or || anchor is substring-matched against the full request URL. The same applied rule action is modifyHeaders that attaches the Entra ID Primary Refresh Token cookie. The Firefox adapter in platform/firefox/js/platform-firefox.js:53 performs a belt-and-braces startsWith(Platform.SSO_URL) check before injecting the header; the Chrome adapter does not. When the extension holds broad host permissions through the optional_host_permissions: ["https://*/*"] declared in platform/chrome/manifest.json:34, a main-frame navigation to a URL whose path embeds https://login.microsoftonline.com/ causes Chrome to attach the PRT cookie to the request to the attacker-controlled host. This vulnerability is fixed in 1.8.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>CVE-2026-8945</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:50.687</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>linux-entra-sso is a browser plugin for Linux to SSO on Microsoft Entra ID. Prior to 1.8.1, platform/chrome/js/platform-chrome.js:69-88 registers a single declarativeNetRequest rule whose urlFilter is Platform.SSO_URL + "/*", i.e. "https://login.microsoftonline.com/*". Chrome's urlFilter without a | or || anchor is substring-matched against the full request URL. The same applied rule action is modifyHeaders that attaches the Entra ID Primary Refresh Token cookie. The Firefox adapter in platform/firefox/js/platform-firefox.js:53 performs a belt-and-braces startsWith(Platform.SSO_URL) check before injecting the header; the Chrome adapter does not. When the extension holds broad host permissions through the optional_host_permissions: ["https://*/*"] declared in platform/chrome/manifest.json:34, a main-frame navigation to a URL whose path embeds https://login.microsoftonline.com/ causes Chrome to attach the PRT cookie to the request to the attacker-controlled host. This vulnerability is fixed in 1.8.1.</t>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Sandbox escape in Firefox and Firefox Focus for Android. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CVE-2026-8946</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:50.800</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CVE-2026-8947</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:50.910</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Use-after-free in the DOM: Bindings (WebIDL) component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CVE-2026-8948</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.027</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Same-origin policy bypass in the DOM: Networking component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CVE-2026-8949</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.140</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Integer overflow in the Widget: Win32 component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CVE-2026-8950</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.257</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Same-origin policy bypass in the Networking: HTTP component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CVE-2026-8951</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.370</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the Toolbar component in Firefox for Android. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CVE-2026-8952</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.480</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Application Update component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CVE-2026-8953</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.593</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to use-after-free in the Disability Access APIs component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CVE-2026-8954</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions, integer overflow in the Audio/Video component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CVE-2026-8955</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.820</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the DOM: Workers component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CVE-2026-8956</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:51.943</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Integer overflow in the Networking: JAR component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CVE-2026-8957</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.057</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Enterprise Policies component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CVE-2026-8958</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.170</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Information disclosure, sandbox escape in the Security: Process Sandboxing component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CVE-2026-8959</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.280</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Sandbox escape due to incorrect boundary conditions in the Widget: Win32 component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CVE-2026-8960</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.383</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Spoofing issue in WebExtensions. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CVE-2026-8961</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.490</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the Form Autofill component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CVE-2026-8962</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.600</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CVE-2026-8963</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.717</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the Web Speech component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CVE-2026-8964</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.823</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Spoofing issue in the Popup Blocker component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CVE-2026-8965</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:52.930</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Information disclosure in the DOM: Security component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CVE-2026-8966</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.043</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Information disclosure in the IP Protection component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CVE-2026-8967</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.160</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Information disclosure in the Graphics: WebGPU component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CVE-2026-8968</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.277</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Denial-of-service due to invalid pointer in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CVE-2026-8969</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.390</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CVE-2026-8970</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.500</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the Security component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CVE-2026-8971</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.633</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Same-origin policy bypass in the Networking: JAR component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CVE-2026-8972</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.753</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Privilege escalation in the WebRTC: Audio/Video component. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CVE-2026-8973</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.860</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CVE-2026-8974</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:53.977</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 140.10 and Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>CVE-2026-8975</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:16:54.090</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.35, Firefox ESR 140.10 and Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5234,11 +5234,7 @@
           <t>2026-05-19T14:16:50.687</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>Sandbox escape in Firefox and Firefox Focus for Android. This vulnerability was fixed in Firefox 151.</t>
@@ -5261,11 +5257,7 @@
           <t>2026-05-19T14:16:50.800</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
@@ -5288,11 +5280,7 @@
           <t>2026-05-19T14:16:50.910</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>Use-after-free in the DOM: Bindings (WebIDL) component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
@@ -5315,11 +5303,7 @@
           <t>2026-05-19T14:16:51.027</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the DOM: Networking component. This vulnerability was fixed in Firefox 151.</t>
@@ -5342,11 +5326,7 @@
           <t>2026-05-19T14:16:51.140</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>Integer overflow in the Widget: Win32 component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5369,11 +5349,7 @@
           <t>2026-05-19T14:16:51.257</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the Networking: HTTP component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5396,11 +5372,7 @@
           <t>2026-05-19T14:16:51.370</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>Spoofing issue in the Toolbar component in Firefox for Android. This vulnerability was fixed in Firefox 151.</t>
@@ -5423,11 +5395,7 @@
           <t>2026-05-19T14:16:51.480</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Privilege escalation in the Application Update component. This vulnerability was fixed in Firefox 151.</t>
@@ -5450,11 +5418,7 @@
           <t>2026-05-19T14:16:51.593</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>Sandbox escape due to use-after-free in the Disability Access APIs component. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
@@ -5477,11 +5441,7 @@
           <t>2026-05-19T14:16:51.700</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions, integer overflow in the Audio/Video component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5504,11 +5464,7 @@
           <t>2026-05-19T14:16:51.820</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>Privilege escalation in the DOM: Workers component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5531,11 +5487,7 @@
           <t>2026-05-19T14:16:51.943</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>Integer overflow in the Networking: JAR component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5558,11 +5510,7 @@
           <t>2026-05-19T14:16:52.057</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Privilege escalation in the Enterprise Policies component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5585,11 +5533,7 @@
           <t>2026-05-19T14:16:52.170</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Information disclosure, sandbox escape in the Security: Process Sandboxing component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5612,11 +5556,7 @@
           <t>2026-05-19T14:16:52.280</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>Sandbox escape due to incorrect boundary conditions in the Widget: Win32 component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5639,11 +5579,7 @@
           <t>2026-05-19T14:16:52.383</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>Spoofing issue in WebExtensions. This vulnerability was fixed in Firefox 151.</t>
@@ -5666,11 +5602,7 @@
           <t>2026-05-19T14:16:52.490</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Spoofing issue in the Form Autofill component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5693,11 +5625,7 @@
           <t>2026-05-19T14:16:52.600</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5720,11 +5648,7 @@
           <t>2026-05-19T14:16:52.717</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>Spoofing issue in the Web Speech component. This vulnerability was fixed in Firefox 151.</t>
@@ -5747,11 +5671,7 @@
           <t>2026-05-19T14:16:52.823</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>Spoofing issue in the Popup Blocker component. This vulnerability was fixed in Firefox 151.</t>
@@ -5774,11 +5694,7 @@
           <t>2026-05-19T14:16:52.930</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>Information disclosure in the DOM: Security component. This vulnerability was fixed in Firefox 151.</t>
@@ -5801,11 +5717,7 @@
           <t>2026-05-19T14:16:53.043</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Information disclosure in the IP Protection component. This vulnerability was fixed in Firefox 151.</t>
@@ -5828,11 +5740,7 @@
           <t>2026-05-19T14:16:53.160</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Information disclosure in the Graphics: WebGPU component. This vulnerability was fixed in Firefox 151.</t>
@@ -5855,11 +5763,7 @@
           <t>2026-05-19T14:16:53.277</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Denial-of-service due to invalid pointer in the Audio/Video: Web Codecs component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5882,11 +5786,7 @@
           <t>2026-05-19T14:16:53.390</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Mitigation bypass in the DOM: Security component. This vulnerability was fixed in Firefox 151.</t>
@@ -5909,11 +5809,7 @@
           <t>2026-05-19T14:16:53.500</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Privilege escalation in the Security component. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -5936,11 +5832,7 @@
           <t>2026-05-19T14:16:53.633</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Same-origin policy bypass in the Networking: JAR component. This vulnerability was fixed in Firefox 151.</t>
@@ -5963,11 +5855,7 @@
           <t>2026-05-19T14:16:53.753</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Privilege escalation in the WebRTC: Audio/Video component. This vulnerability was fixed in Firefox 151.</t>
@@ -5990,11 +5878,7 @@
           <t>2026-05-19T14:16:53.860</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151.</t>
@@ -6017,11 +5901,7 @@
           <t>2026-05-19T14:16:53.977</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>Memory safety bugs present in Firefox ESR 140.10 and Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151 and Firefox ESR 140.11.</t>
@@ -6044,14 +5924,37 @@
           <t>2026-05-19T14:16:54.090</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Memory safety bugs present in Firefox ESR 115.35, Firefox ESR 140.10 and Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CVE-2026-8706</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-05-19T16:16:22.580</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Memory safety bugs present in Firefox ESR 115.35, Firefox ESR 140.10 and Firefox 150. Some of these bugs showed evidence of memory corruption and we presume that with enough effort some of these could have been exploited to run arbitrary code. This vulnerability was fixed in Firefox 151, Firefox ESR 115.36, and Firefox ESR 140.11.</t>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Firefox for iOS hosted Reader mode on an unauthenticated local web server, allowing another application on the same device to request arbitrary URLs and receive the response rendered with the signed-in user's cookies. This vulnerability was fixed in Firefox for iOS 151.0.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5947,14 +5947,37 @@
           <t>2026-05-19T16:16:22.580</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Firefox for iOS hosted Reader mode on an unauthenticated local web server, allowing another application on the same device to request arbitrary URLs and receive the response rendered with the signed-in user's cookies. This vulnerability was fixed in Firefox for iOS 151.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CVE-2026-9078</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-05-25T15:16:22.970</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Firefox for iOS hosted Reader mode on an unauthenticated local web server, allowing another application on the same device to request arbitrary URLs and receive the response rendered with the signed-in user's cookies. This vulnerability was fixed in Firefox for iOS 151.0.</t>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Firefox for iOS displayed specially crafted right-to-left (RTL) and internationalized domain names (IDNs) incorrectly in link preview UI surfaces. A crafted RTL hostname could visually reorder portions of the displayed domain, causing attacker-controlled sites to appear as trusted origins. This vulnerability was fixed in Firefox for iOS 151.1.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5970,14 +5970,64 @@
           <t>2026-05-25T15:16:22.970</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Firefox for iOS displayed specially crafted right-to-left (RTL) and internationalized domain names (IDNs) incorrectly in link preview UI surfaces. A crafted RTL hostname could visually reorder portions of the displayed domain, causing attacker-controlled sites to appear as trusted origins. This vulnerability was fixed in Firefox for iOS 151.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CVE-2026-9308</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:16:33.523</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Firefox for iOS displayed specially crafted right-to-left (RTL) and internationalized domain names (IDNs) incorrectly in link preview UI surfaces. A crafted RTL hostname could visually reorder portions of the displayed domain, causing attacker-controlled sites to appear as trusted origins. This vulnerability was fixed in Firefox for iOS 151.1.</t>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Firefox for iOS Reader View replaced page content in its HTML template before replacing other internal placeholders. A malicious page could include a placeholder string that was later substituted with JSON-LD data, potentially resulting in arbitrary JavaScript execution. This vulnerability was fixed in Firefox for iOS 151.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CVE-2026-9309</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:16:33.623</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Firefox for iOS Reader View did not properly escape HTML tags in JSON-LD metadata. A malicious page could inject markup that changed Reader View behavior and leaked sensitive URL parameters. These parameters could then be used to access internal pages, potentially resulting in arbitrary JavaScript execution in an internal origin. This vulnerability was fixed in Firefox for iOS 151.2.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E236"/>
+  <dimension ref="A1:E238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5993,11 +5993,7 @@
           <t>2026-06-01T13:16:33.523</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>Firefox for iOS Reader View replaced page content in its HTML template before replacing other internal placeholders. A malicious page could include a placeholder string that was later substituted with JSON-LD data, potentially resulting in arbitrary JavaScript execution. This vulnerability was fixed in Firefox for iOS 151.2.</t>
@@ -6020,14 +6016,64 @@
           <t>2026-06-01T13:16:33.623</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Firefox for iOS Reader View did not properly escape HTML tags in JSON-LD metadata. A malicious page could inject markup that changed Reader View behavior and leaked sensitive URL parameters. These parameters could then be used to access internal pages, potentially resulting in arbitrary JavaScript execution in an internal origin. This vulnerability was fixed in Firefox for iOS 151.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CVE-2026-10701</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-06-02T20:16:33.227</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Firefox for iOS Reader View did not properly escape HTML tags in JSON-LD metadata. A malicious page could inject markup that changed Reader View behavior and leaked sensitive URL parameters. These parameters could then be used to access internal pages, potentially resulting in arbitrary JavaScript execution in an internal origin. This vulnerability was fixed in Firefox for iOS 151.2.</t>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Incorrect boundary conditions in the Graphics: Text component. This vulnerability was fixed in Firefox 151.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CVE-2026-10702</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-06-02T20:16:33.377</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 151.0.3.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E238"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6039,11 +6039,7 @@
           <t>2026-06-02T20:16:33.227</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>Incorrect boundary conditions in the Graphics: Text component. This vulnerability was fixed in Firefox 151.0.3.</t>
@@ -6066,14 +6062,37 @@
           <t>2026-06-02T20:16:33.377</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 151.0.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>CVE-2023-43686</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-06-09T19:16:41.907</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>JIT miscompilation in the JavaScript Engine: JIT component. This vulnerability was fixed in Firefox 151.0.3.</t>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Malwarebytes 4.x and 5.x (and Nebula 2020-10-21 and later). A large number of Firefox preference files can cause the parser to ignore other browser configuration files, leading to a denial of service.</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6085,14 +6085,37 @@
           <t>2026-06-09T19:16:41.907</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>An issue was discovered in Malwarebytes 4.x and 5.x (and Nebula 2020-10-21 and later). A large number of Firefox preference files can cause the parser to ignore other browser configuration files, leading to a denial of service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CVE-2026-45173</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-06-11T22:16:57.470</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>An issue was discovered in Malwarebytes 4.x and 5.x (and Nebula 2020-10-21 and later). A large number of Firefox preference files can cause the parser to ignore other browser configuration files, leading to a denial of service.</t>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Idira Identity Browser Extension (Chrome, Firefox, and Edge builds) versions prior to 26.8.1 exhibit an origin validation flaw within its internal web-page verification routines. If an authenticated user navigates to a specially crafted webpage, this interaction could potentially allow a remote attacker to trigger unauthorized application interaction or execution parameters within the context of that authenticated browser session. CyberArk Security Bulletin: CA26-21</t>
         </is>
       </c>
     </row>

--- a/relatorio_cves_recentes.xlsx
+++ b/relatorio_cves_recentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E240"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,14 +6108,38 @@
           <t>2026-06-11T22:16:57.470</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Idira Identity Browser Extension (Chrome, Firefox, and Edge builds) versions prior to 26.8.1 exhibit an origin validation flaw within its internal web-page verification routines. If an authenticated user navigates to a specially crafted webpage, this interaction could potentially allow a remote attacker to trigger unauthorized application interaction or execution parameters within the context of that authenticated browser session. CyberArk Security Bulletin: CA26-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Mozilla Firefox</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CVE-2026-12068</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-06-12T23:16:33.553</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Idira Identity Browser Extension (Chrome, Firefox, and Edge builds) versions prior to 26.8.1 exhibit an origin validation flaw within its internal web-page verification routines. If an authenticated user navigates to a specially crafted webpage, this interaction could potentially allow a remote attacker to trigger unauthorized application interaction or execution parameters within the context of that authenticated browser session. CyberArk Security Bulletin: CA26-21</t>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Information disclosure vulnerability in Avira Password Manager when used with Mozilla Firefox may allow a remote attacker operating a cross-origin iframe to obtain credentials autofilled for the parent web page via incorrect autofill field selection.
+This issue affects Avira Password Manager when used with Mozilla Firefox on Windows, macOS, and Linux.</t>
         </is>
       </c>
     </row>
